--- a/CPS_Apr_may_data.xlsx
+++ b/CPS_Apr_may_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\cps_dashboard\cps_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2C03CE-3E26-4CAA-9193-D0AF507DECE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8898F68C-150D-4A6B-9697-614D8C3F0E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F90CE2D4-B827-42A1-8AF6-12FAF1C8B344}"/>
   </bookViews>
@@ -773,6 +773,9 @@
   <sheetPr filterMode="1"/>
   <dimension ref="A1:F1928"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="6" max="6" width="28.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
